--- a/data/trans_dic/IP19C06-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP19C06-Clase-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -526,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que en su última visita al dentista fue por tratamiento de las enfermedades de las encías</t>
+          <t>Menores que en su última visita al dentista fue por tratamiento de las enfermedades de las encías (tasa de respuesta: 99,46%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0; 2,39</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0; 2,82</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0; 3,09</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,85; 10,46</t>
+          <t>1,69; 10,68</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0; 2,55</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0; 3,09</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0; 2,62</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0; 1,6</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0; 1,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0; 1,49</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0; 1,43</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,66; 4,62</t>
+          <t>0,67; 4,18</t>
         </is>
       </c>
     </row>
@@ -856,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0; 3,09</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,6</t>
+          <t>0,0; 5,15</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0; 2,39</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,31</t>
+          <t>0,0; 5,31</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0; 3,36</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,92</t>
+          <t>0,0; 5,12</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0; 2,49</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,47</t>
+          <t>0,0; 6,18</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0; 1,62</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,89</t>
+          <t>0,0; 3,33</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0; 1,23</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,29</t>
+          <t>0,0; 4,59</t>
         </is>
       </c>
     </row>
@@ -996,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 3,61</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,39</t>
+          <t>0,0; 9,75</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 4,16</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 4,66</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 2,36</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 3,19</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 3,82</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0; 4,07</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0; 1,44</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,29</t>
+          <t>0,0; 4,94</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0; 2,02</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0; 2,2</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0; 1,3</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,85</t>
+          <t>0,0; 4,33</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0; 1,17</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,88</t>
+          <t>0,0; 3,17</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0; 1,31</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0; 1,36</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0; 1,33</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0; 1,3</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,66</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,85</t>
+          <t>0,0; 1,9</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,63</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,64</t>
+          <t>0,0; 1,61</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0; 2,34</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0; 1,62</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,75</t>
+          <t>0,0; 5,66</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,25</t>
+          <t>0,0; 5,08</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,8</t>
+          <t>0,0; 3,78</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,66</t>
+          <t>0,0; 7,41</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0; 1,9</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0; 1,77</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,37</t>
+          <t>0,0; 2,12</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,49</t>
+          <t>0,0; 3,68</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,71</t>
+          <t>0,0; 3,25</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,76</t>
+          <t>0,0; 1,58</t>
         </is>
       </c>
     </row>
@@ -1416,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 3,14</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,54</t>
+          <t>0,0; 12,81</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,84</t>
+          <t>0,0; 9,76</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 3,04</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,42</t>
+          <t>0,0; 7,9</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0; 3,54</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 4,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,49</t>
+          <t>0,0; 13,48</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,58</t>
+          <t>0,0; 4,15</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,73</t>
+          <t>0,0; 7,39</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,83</t>
+          <t>0,0; 5,3</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,96</t>
+          <t>0,0; 7,56</t>
         </is>
       </c>
     </row>
@@ -1556,42 +1557,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0; 0,4</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,34; 2,45</t>
+          <t>0,3; 2,06</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,39</t>
+          <t>0,0; 1,45</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,71; 2,78</t>
+          <t>0,77; 2,72</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,28</t>
+          <t>0,0; 1,47</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,18; 1,76</t>
+          <t>0,18; 1,85</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0; 0,4</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,5</t>
+          <t>0,0; 1,74</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -1601,17 +1602,17 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>0,32; 1,45</t>
+          <t>0,39; 1,51</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,72</t>
+          <t>0,0; 0,7</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>0,48; 1,73</t>
+          <t>0,5; 1,77</t>
         </is>
       </c>
     </row>
@@ -1638,4 +1639,1622 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que en su última visita al dentista fue por tratamiento de las enfermedades de las encías (tasa de respuesta: 99,46%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="n"/>
+      <c r="M1" s="3" t="n"/>
+      <c r="N1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Grupo I y II</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>3302</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>3302</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>1212; 7663</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>1124; 7012</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Grupo III</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>430</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>808</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>624</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>1045</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>1054</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>1853</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>0; 2447</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3332</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>0; 2720</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>0; 4421</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3353</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>0; 6170</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Grupo IV y V</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>1283</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>1283</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4070</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4027</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VI</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>698</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>1108</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>698</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>1108</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>0; 3949</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>0; 3521</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>0; 3592</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>0; 3836</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VII</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>771</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>540</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>525</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>1599</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>525</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>1599</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>771</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>540</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>0; 3912</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>0; 3479</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>0; 2650</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>0; 5456</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>0; 2644</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>0; 5733</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>0; 4637</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>0; 2719</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>No ha trabajado</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>818</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>617</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>695</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>1332</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>695</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>818</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>617</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>1332</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>0; 3292</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>0; 3182</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>0; 2823</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>0; 5947</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>0; 3142</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>0; 4670</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>0; 3434</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>0; 6729</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>3230</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>1388</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>5758</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>1219</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>2223</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>2377</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>1219</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>5452</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>1388</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>8135</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>1009; 6944</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>0; 4974</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>2960; 10540</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>0; 5038</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>622; 6336</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>0; 8310</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>0; 4068</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>2627; 10233</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>0; 4817</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>4361; 15295</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP19C06-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP19C06-Clase-trans_dic.xlsx
@@ -732,7 +732,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,69; 10,68</t>
+          <t>1,62; 10,43</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -772,7 +772,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,67; 4,18</t>
+          <t>0,69; 4,5</t>
         </is>
       </c>
     </row>
@@ -862,7 +862,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,15</t>
+          <t>0,0; 4,72</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,31</t>
+          <t>0,0; 7,6</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -882,7 +882,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,12</t>
+          <t>0,0; 6,7</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -892,7 +892,7 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,18</t>
+          <t>0,0; 7,83</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -902,7 +902,7 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,33</t>
+          <t>0,0; 3,92</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
@@ -912,7 +912,7 @@
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,59</t>
+          <t>0,0; 4,36</t>
         </is>
       </c>
     </row>
@@ -1002,7 +1002,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,75</t>
+          <t>0,0; 10,79</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,94</t>
+          <t>0,0; 5,31</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
@@ -1142,7 +1142,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,33</t>
+          <t>0,0; 3,83</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1152,7 +1152,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,17</t>
+          <t>0,0; 3,2</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1182,7 +1182,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,9</t>
+          <t>0,0; 1,84</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -1192,7 +1192,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,61</t>
+          <t>0,0; 1,75</t>
         </is>
       </c>
     </row>
@@ -1287,22 +1287,22 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,66</t>
+          <t>0,0; 5,64</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,08</t>
+          <t>0,0; 4,17</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,78</t>
+          <t>0,0; 3,84</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,41</t>
+          <t>0,0; 7,64</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1317,22 +1317,22 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,12</t>
+          <t>0,0; 2,43</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,68</t>
+          <t>0,0; 3,61</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,25</t>
+          <t>0,0; 2,99</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,58</t>
+          <t>0,0; 1,76</t>
         </is>
       </c>
     </row>
@@ -1422,12 +1422,12 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,81</t>
+          <t>0,0; 13,2</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,76</t>
+          <t>0,0; 10,33</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1437,7 +1437,7 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,9</t>
+          <t>0,0; 7,84</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1452,27 +1452,27 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,48</t>
+          <t>0,0; 15,12</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,15</t>
+          <t>0,0; 4,05</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,39</t>
+          <t>0,0; 6,95</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,3</t>
+          <t>0,0; 3,91</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,56</t>
+          <t>0,0; 7,3</t>
         </is>
       </c>
     </row>
@@ -1562,27 +1562,27 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,3; 2,06</t>
+          <t>0,34; 2,22</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,45</t>
+          <t>0,0; 1,31</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,77; 2,72</t>
+          <t>0,72; 2,74</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,47</t>
+          <t>0,0; 1,19</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,18; 1,85</t>
+          <t>0,18; 1,68</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -1592,27 +1592,27 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,74</t>
+          <t>0,0; 1,68</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,61</t>
+          <t>0,0; 0,64</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>0,39; 1,51</t>
+          <t>0,39; 1,64</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,7</t>
+          <t>0,0; 0,63</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>0,5; 1,77</t>
+          <t>0,48; 1,64</t>
         </is>
       </c>
     </row>
@@ -1942,7 +1942,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1212; 7663</t>
+          <t>1161; 7484</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -1982,7 +1982,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>1124; 7012</t>
+          <t>1153; 7547</t>
         </is>
       </c>
     </row>
@@ -2140,7 +2140,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 2447</t>
+          <t>0; 2243</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -2150,7 +2150,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 3332</t>
+          <t>0; 4767</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -2160,7 +2160,7 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 2720</t>
+          <t>0; 3554</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -2170,7 +2170,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0; 4421</t>
+          <t>0; 5605</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -2180,7 +2180,7 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0; 3353</t>
+          <t>0; 3945</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
@@ -2190,7 +2190,7 @@
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0; 6170</t>
+          <t>0; 5859</t>
         </is>
       </c>
     </row>
@@ -2348,7 +2348,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 4070</t>
+          <t>0; 4502</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -2388,7 +2388,7 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>0; 4027</t>
+          <t>0; 4330</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
@@ -2556,7 +2556,7 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 3949</t>
+          <t>0; 3495</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -2566,7 +2566,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 3521</t>
+          <t>0; 3552</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>0; 3592</t>
+          <t>0; 3484</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
@@ -2606,7 +2606,7 @@
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>0; 3836</t>
+          <t>0; 4163</t>
         </is>
       </c>
     </row>
@@ -2769,22 +2769,22 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0; 3912</t>
+          <t>0; 3899</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>0; 3479</t>
+          <t>0; 2857</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>0; 2650</t>
+          <t>0; 2691</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0; 5456</t>
+          <t>0; 5627</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -2799,22 +2799,22 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>0; 2644</t>
+          <t>0; 3029</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>0; 5733</t>
+          <t>0; 5634</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>0; 4637</t>
+          <t>0; 4274</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>0; 2719</t>
+          <t>0; 3022</t>
         </is>
       </c>
     </row>
@@ -2972,12 +2972,12 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 3292</t>
+          <t>0; 3391</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0; 3182</t>
+          <t>0; 3367</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
@@ -2987,7 +2987,7 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0; 2823</t>
+          <t>0; 2801</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -3002,27 +3002,27 @@
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0; 5947</t>
+          <t>0; 6671</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0; 3142</t>
+          <t>0; 3066</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>0; 4670</t>
+          <t>0; 4395</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>0; 3434</t>
+          <t>0; 2535</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>0; 6729</t>
+          <t>0; 6496</t>
         </is>
       </c>
     </row>
@@ -3180,27 +3180,27 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>1009; 6944</t>
+          <t>1132; 7476</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>0; 4974</t>
+          <t>0; 4476</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>2960; 10540</t>
+          <t>2769; 10582</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>0; 5038</t>
+          <t>0; 4070</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>622; 6336</t>
+          <t>619; 5778</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -3210,27 +3210,27 @@
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>0; 8310</t>
+          <t>0; 8038</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>0; 4068</t>
+          <t>0; 4253</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>2627; 10233</t>
+          <t>2648; 11168</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>0; 4817</t>
+          <t>0; 4336</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>4361; 15295</t>
+          <t>4188; 14220</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP19C06-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP19C06-Clase-trans_dic.xlsx
@@ -533,7 +533,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>2,07%</t>
         </is>
       </c>
     </row>
@@ -732,7 +732,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,62; 10,43</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -752,7 +752,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>1,97; 10,97</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -772,7 +772,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,69; 4,5</t>
+          <t>0,67; 4,83</t>
         </is>
       </c>
     </row>
@@ -794,29 +794,29 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
+          <t>1,17%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>1,37%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
           <t>0,91%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>1,29%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>1,17%</t>
-        </is>
-      </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,32%</t>
         </is>
       </c>
     </row>
@@ -862,7 +862,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,72</t>
+          <t>0,0; 5,92</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,6</t>
+          <t>0,0; 8,15</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -882,7 +882,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,7</t>
+          <t>0,0; 4,6</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -892,7 +892,7 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,83</t>
+          <t>0,0; 6,18</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -902,7 +902,7 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,92</t>
+          <t>0,0; 3,89</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
@@ -912,7 +912,7 @@
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,36</t>
+          <t>0,0; 4,06</t>
         </is>
       </c>
     </row>
@@ -934,27 +934,27 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
           <t>3,07%</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1002,7 +1002,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,79</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -1022,7 +1022,7 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 10,39</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,31</t>
+          <t>0,0; 5,29</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
@@ -1074,29 +1074,29 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
           <t>0,77%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>1,0%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,45%</t>
         </is>
       </c>
     </row>
@@ -1142,7 +1142,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,83</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1152,7 +1152,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,2</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 3,85</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1172,7 +1172,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 3,74</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1182,7 +1182,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,84</t>
+          <t>0,0; 1,85</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -1192,7 +1192,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,75</t>
+          <t>0,0; 1,64</t>
         </is>
       </c>
     </row>
@@ -1209,42 +1209,42 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
           <t>1,11%</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>0,79%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>0,75%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>2,17%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,29%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 4,8</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 6,66</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,64</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,17</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,84</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,64</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 6,75</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 3,74</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,43</t>
+          <t>0,0; 2,37</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,61</t>
+          <t>0,0; 3,49</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,99</t>
+          <t>0,0; 2,71</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,76</t>
+          <t>0,0; 1,72</t>
         </is>
       </c>
     </row>
@@ -1349,42 +1349,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>1,46%</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
           <t>3,19%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>1,89%</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>1,94%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>0,7%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 8,42</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,2</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,33</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 7,39</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,84</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 15,54</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 9,84</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,12</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,05</t>
+          <t>0,0; 4,58</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,95</t>
+          <t>0,0; 6,73</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,91</t>
+          <t>0,0; 4,83</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,3</t>
+          <t>0,0; 4,94</t>
         </is>
       </c>
     </row>
@@ -1489,42 +1489,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
+          <t>0,65%</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>0,35%</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
           <t>0,96%</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>0,41%</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>1,49%</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>0,36%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>0,65%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,86%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 1,28</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,34; 2,22</t>
+          <t>0,18; 1,76</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,31</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,72; 2,74</t>
+          <t>0,0; 1,06</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,19</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,18; 1,68</t>
+          <t>0,34; 2,45</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 1,39</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,68</t>
+          <t>0,69; 2,76</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,64</t>
+          <t>0,0; 0,61</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>0,39; 1,64</t>
+          <t>0,32; 1,45</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,63</t>
+          <t>0,0; 0,72</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>0,48; 1,64</t>
+          <t>0,45; 1,55</t>
         </is>
       </c>
     </row>
@@ -1675,7 +1675,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1683,7 +1683,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -1806,27 +1806,27 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>5</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -1874,7 +1874,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3302</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3349</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1914,7 +1914,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>3302</t>
+          <t>3349</t>
         </is>
       </c>
     </row>
@@ -1942,7 +1942,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1161; 7484</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -1962,7 +1962,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>1407; 7842</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -1982,7 +1982,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>1153; 7547</t>
+          <t>1087; 7824</t>
         </is>
       </c>
     </row>
@@ -2072,29 +2072,29 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
+          <t>624</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>964</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
           <t>430</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>808</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>624</t>
-        </is>
-      </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
           <t>0</t>
@@ -2102,7 +2102,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>1045</t>
+          <t>821</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2122,7 +2122,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>1853</t>
+          <t>1785</t>
         </is>
       </c>
     </row>
@@ -2140,7 +2140,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 2243</t>
+          <t>0; 3144</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -2150,7 +2150,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 4767</t>
+          <t>0; 5737</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -2160,7 +2160,7 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 3554</t>
+          <t>0; 2184</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -2170,7 +2170,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0; 5605</t>
+          <t>0; 4030</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -2180,7 +2180,7 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0; 3945</t>
+          <t>0; 3915</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
@@ -2190,7 +2190,7 @@
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0; 5859</t>
+          <t>0; 5502</t>
         </is>
       </c>
     </row>
@@ -2212,27 +2212,27 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -2280,27 +2280,27 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
           <t>1283</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -2348,7 +2348,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 4502</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -2368,7 +2368,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 4335</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -2388,7 +2388,7 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>0; 4330</t>
+          <t>0; 4309</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
@@ -2420,37 +2420,37 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -2488,29 +2488,29 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
           <t>698</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>1108</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
           <t>0</t>
@@ -2518,7 +2518,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1041</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>1108</t>
+          <t>1041</t>
         </is>
       </c>
     </row>
@@ -2556,7 +2556,7 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 3495</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -2566,7 +2566,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 3552</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2576,7 +2576,7 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3509</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 4083</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>0; 3484</t>
+          <t>0; 3501</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
@@ -2606,7 +2606,7 @@
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>0; 4163</t>
+          <t>0; 3794</t>
         </is>
       </c>
     </row>
@@ -2623,42 +2623,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -2691,54 +2691,54 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>525</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1599</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
           <t>771</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>540</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>478</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>525</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
         <is>
           <t>1599</t>
         </is>
       </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>525</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>1599</t>
-        </is>
-      </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
           <t>771</t>
@@ -2746,7 +2746,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>540</t>
+          <t>478</t>
         </is>
       </c>
     </row>
@@ -2759,62 +2759,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3362</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 4904</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0; 3899</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>0; 2857</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>0; 2691</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0; 5627</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 4669</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 2584</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>0; 3029</t>
+          <t>0; 2961</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>0; 5634</t>
+          <t>0; 5442</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>0; 4274</t>
+          <t>0; 3875</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>0; 3022</t>
+          <t>0; 2811</t>
         </is>
       </c>
     </row>
@@ -2831,42 +2831,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="I19" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -2899,49 +2899,49 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>695</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>641</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
           <t>818</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="I20" s="2" t="inlineStr">
         <is>
           <t>617</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>695</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>1332</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>695</t>
-        </is>
-      </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
           <t>818</t>
@@ -2954,7 +2954,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>1332</t>
+          <t>641</t>
         </is>
       </c>
     </row>
@@ -2967,62 +2967,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3009</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 3391</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0; 3367</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3232</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0; 2801</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3993</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3208</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0; 6671</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0; 3066</t>
+          <t>0; 3471</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>0; 4395</t>
+          <t>0; 4251</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>0; 2535</t>
+          <t>0; 3128</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>0; 6496</t>
+          <t>0; 4502</t>
         </is>
       </c>
     </row>
@@ -3039,42 +3039,42 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="I22" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="J22" s="2" t="inlineStr">
         <is>
           <t>9</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
@@ -3107,49 +3107,49 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1219</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
+          <t>2223</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>1605</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
           <t>3230</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="I23" s="2" t="inlineStr">
         <is>
           <t>1388</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>5758</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>5689</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>1219</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>2223</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>2377</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>1219</t>
-        </is>
-      </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
           <t>5452</t>
@@ -3162,7 +3162,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>8135</t>
+          <t>7294</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 4366</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>1132; 7476</t>
+          <t>621; 6040</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>0; 4476</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>2769; 10582</t>
+          <t>0; 4845</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>0; 4070</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>619; 5778</t>
+          <t>1132; 8261</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 4750</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>0; 8038</t>
+          <t>2702; 10806</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>0; 4253</t>
+          <t>0; 4026</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>2648; 11168</t>
+          <t>2197; 9853</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>0; 4336</t>
+          <t>0; 4985</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>4188; 14220</t>
+          <t>3834; 13111</t>
         </is>
       </c>
     </row>
